--- a/results/monthly_investor_report_2026-10-08.xlsx
+++ b/results/monthly_investor_report_2026-10-08.xlsx
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2211403098513339</v>
+        <v>0.2211403098513338</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22114.03098513339</v>
+        <v>22114.03098513338</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.0191938585275912</v>
@@ -984,13 +984,13 @@
         <v>424.4535822034185</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>216.4767693305947</v>
+        <v>216.4767693305948</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>198.3527119886738</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.2902180977690499</v>
+        <v>0.2902180977690493</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1370,7 +1370,7 @@
         <v>401</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0205580539159817</v>
+        <v>-0.0205580539159813</v>
       </c>
       <c r="F8" s="16" t="n">
         <v>0.019028938484348</v>
@@ -1379,7 +1379,7 @@
         <v>0.06844627048378669</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>392.7562203796913</v>
+        <v>392.7562203796915</v>
       </c>
       <c r="I8" s="15" t="n">
         <v>408.6306043322236</v>
@@ -1439,7 +1439,7 @@
         <v>198.3527119886738</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>216.4767693305947</v>
+        <v>216.4767693305948</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>227.0649219385337</v>
@@ -1484,7 +1484,7 @@
         <v>392.25</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>-0.08597935286307549</v>
+        <v>-0.0859793528630754</v>
       </c>
       <c r="F10" s="19" t="n">
         <v>0.0195381803197951</v>
@@ -1547,7 +1547,7 @@
         <v>0.0417061216022127</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.1388396310918183</v>
+        <v>0.1388396310918185</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>72.11869692957994</v>
@@ -1556,7 +1556,7 @@
         <v>77.50293703672203</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>84.72967029096264</v>
+        <v>84.72967029096267</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>70.68000144958496</v>
@@ -1601,10 +1601,10 @@
         <v>-0.052434175232511</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0.003753763602968</v>
+        <v>0.0037537636029683</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.0701777996871968</v>
+        <v>0.0701777996871966</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>269.3455856901587</v>
@@ -1613,7 +1613,7 @@
         <v>285.3170073041437</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>304.1980395610857</v>
+        <v>304.1980395610856</v>
       </c>
       <c r="K12" s="15" t="n">
         <v>269.3455856901587</v>
@@ -1655,13 +1655,13 @@
         <v>135.6000061035156</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.0537067277155769</v>
+        <v>-0.0537067277155768</v>
       </c>
       <c r="F13" s="22" t="n">
         <v>-0.0194552529182879</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1090029643218295</v>
+        <v>0.1090029643218296</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>128.3173734974835</v>
@@ -1715,7 +1715,7 @@
         <v>-0.07126395669746011</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.0091399766450234</v>
+        <v>-0.0091399766450236</v>
       </c>
       <c r="G14" s="22" t="n">
         <v>0.0415042015350602</v>
@@ -1724,7 +1724,7 @@
         <v>249.8299956483832</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>266.5413462824887</v>
+        <v>266.5413462824886</v>
       </c>
       <c r="J14" s="21" t="n">
         <v>280.1646302129312</v>
@@ -1799,7 +1799,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1893,7 +1893,7 @@
         <v>-0.0563137182802316</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.08302253368216519</v>
+        <v>0.083022533682165</v>
       </c>
       <c r="G4" s="16" t="n">
         <v>0.1737397162419263</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>-0.0505140956902753</v>
+        <v>-0.0505140956902752</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.1016597019423535</v>
+        <v>0.1016597019423537</v>
       </c>
       <c r="G5" s="19" t="n">
         <v>0.09259259549969311</v>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="J8" s="16" t="n">
-        <v>0.0186262496527776</v>
+        <v>0.0186262496527777</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>0.003753763602968</v>
+        <v>0.0037537636029683</v>
       </c>
     </row>
     <row r="9">
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.0256830236584199</v>
+        <v>-0.0256830236584196</v>
       </c>
       <c r="F9" s="24" t="n">
         <v>0.0147979643368136</v>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.07600211160664</v>
+        <v>-0.0760021116066399</v>
       </c>
       <c r="F10" s="24" t="n">
         <v>-0.0193370165745856</v>
@@ -2168,7 +2168,7 @@
         <v>0.0201048370906429</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>0.0588821519160343</v>
+        <v>0.058882151916034</v>
       </c>
     </row>
     <row r="11">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.0152502117516968</v>
+        <v>0.0152502117516969</v>
       </c>
       <c r="K12" s="24" t="n">
         <v>0.0007363095911598</v>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.0157171518226982</v>
+        <v>-0.0157171518226979</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>-0.0635514303902599</v>
+        <v>-0.06355143039025971</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>-0.07734808143556821</v>
+        <v>-0.07734808143556809</v>
       </c>
       <c r="H13" s="24" t="n">
         <v>-0.2330852114160289</v>
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>-0.0634596530382676</v>
+        <v>-0.0634596530382678</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>-0.094059477926595</v>
+        <v>-0.09405947792659509</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>0.2341201160407111</v>
+        <v>0.2341201160407109</v>
       </c>
       <c r="H14" s="26" t="n">
         <v>-0.222405128083297</v>
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="J16" s="28" t="n">
-        <v>0.0186775555598611</v>
+        <v>0.018677555559861</v>
       </c>
       <c r="K16" s="28" t="n">
         <v>-0.0194552529182879</v>
@@ -2452,10 +2452,10 @@
         <v>-0.2030888149171456</v>
       </c>
       <c r="F17" s="26" t="n">
-        <v>0.0672181606413582</v>
+        <v>0.0672181606413584</v>
       </c>
       <c r="G17" s="26" t="n">
-        <v>-0.010546558689646</v>
+        <v>-0.0105465586896457</v>
       </c>
       <c r="H17" s="26" t="n">
         <v>0.0260650374925286</v>
@@ -2512,7 +2512,7 @@
         <v>0.0254645426742394</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>-0.0091399766450234</v>
+        <v>-0.0091399766450236</v>
       </c>
     </row>
     <row r="19">
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="J19" s="26" t="n">
-        <v>0.0316386844276283</v>
+        <v>0.0316386844276284</v>
       </c>
       <c r="K19" s="26" t="n">
         <v>0.0478184312002618</v>
@@ -2581,7 +2581,7 @@
         <v>-0.1569326977205356</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>-0.1293738284887817</v>
+        <v>-0.1293738284887816</v>
       </c>
       <c r="G20" s="26" t="n">
         <v>-0.1448316943799105</v>
@@ -2631,7 +2631,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2750,7 +2750,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3001,7 +3001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3126,7 +3126,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3227,7 +3227,7 @@
         <v>212.3999938964844</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>0.07817255785017441</v>
+        <v>0.07817255785017463</v>
       </c>
       <c r="F5" s="29" t="n">
         <v>227196.4023002572</v>

--- a/results/monthly_investor_report_2026-10-08.xlsx
+++ b/results/monthly_investor_report_2026-10-08.xlsx
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1799,7 +1799,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2631,7 +2631,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2750,7 +2750,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3001,7 +3001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3126,7 +3126,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
